--- a/artfynd/A 38599-2025 artfynd.xlsx
+++ b/artfynd/A 38599-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>13762756</v>
       </c>
       <c r="B2" t="n">
-        <v>60381</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589686.9552475755</v>
+        <v>589687</v>
       </c>
       <c r="R2" t="n">
-        <v>6497975.401519065</v>
+        <v>6497975</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1977-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1977-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -801,12 +786,7 @@
         <v>2270211</v>
       </c>
       <c r="B3" t="n">
-        <v>96242</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589731.3752118053</v>
+        <v>589731</v>
       </c>
       <c r="R3" t="n">
-        <v>6498086.900005973</v>
+        <v>6498087</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -871,19 +851,9 @@
           <t>1980-05-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1990-06-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,12 +887,7 @@
         <v>101810014</v>
       </c>
       <c r="B4" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589703.3068038234</v>
+        <v>589703</v>
       </c>
       <c r="R4" t="n">
-        <v>6498081.563999754</v>
+        <v>6498082</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,19 +957,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,6 +988,113 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110056828</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fridlund 280 m NO, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>589686</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6498088</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Östra Husby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Översilad betesmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Göran Göransson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Göran Göransson, Göran Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38599-2025 artfynd.xlsx
+++ b/artfynd/A 38599-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13762756</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
           <t>Äldre fynd i Östergötlands flora x</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2270211</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101810014</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,8 +1115,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110056828</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>